--- a/artfynd/A 53366-2024 artfynd.xlsx
+++ b/artfynd/A 53366-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121150398</v>
       </c>
       <c r="B2" t="n">
-        <v>78334</v>
+        <v>78337</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>121150399</v>
       </c>
       <c r="B3" t="n">
-        <v>91979</v>
+        <v>91989</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53366-2024 artfynd.xlsx
+++ b/artfynd/A 53366-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150398</v>
+        <v>121150399</v>
       </c>
       <c r="B2" t="n">
-        <v>78337</v>
+        <v>91989</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>749391</v>
+        <v>749471</v>
       </c>
       <c r="R2" t="n">
-        <v>7381398</v>
+        <v>7381290</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150399</v>
+        <v>121150398</v>
       </c>
       <c r="B3" t="n">
-        <v>91989</v>
+        <v>78337</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>749471</v>
+        <v>749391</v>
       </c>
       <c r="R3" t="n">
-        <v>7381290</v>
+        <v>7381398</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 53366-2024 artfynd.xlsx
+++ b/artfynd/A 53366-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121150399</v>
       </c>
       <c r="B2" t="n">
-        <v>91989</v>
+        <v>92001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>121150398</v>
       </c>
       <c r="B3" t="n">
-        <v>78337</v>
+        <v>78340</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53366-2024 artfynd.xlsx
+++ b/artfynd/A 53366-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150399</v>
+        <v>121150398</v>
       </c>
       <c r="B2" t="n">
-        <v>92001</v>
+        <v>78340</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>749471</v>
+        <v>749391</v>
       </c>
       <c r="R2" t="n">
-        <v>7381290</v>
+        <v>7381398</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150398</v>
+        <v>121150399</v>
       </c>
       <c r="B3" t="n">
-        <v>78340</v>
+        <v>92002</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>749391</v>
+        <v>749471</v>
       </c>
       <c r="R3" t="n">
-        <v>7381398</v>
+        <v>7381290</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 53366-2024 artfynd.xlsx
+++ b/artfynd/A 53366-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150398</v>
+        <v>121150399</v>
       </c>
       <c r="B2" t="n">
-        <v>78340</v>
+        <v>92005</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>749391</v>
+        <v>749471</v>
       </c>
       <c r="R2" t="n">
-        <v>7381398</v>
+        <v>7381290</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150399</v>
+        <v>121150398</v>
       </c>
       <c r="B3" t="n">
-        <v>92002</v>
+        <v>78343</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>749471</v>
+        <v>749391</v>
       </c>
       <c r="R3" t="n">
-        <v>7381290</v>
+        <v>7381398</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 53366-2024 artfynd.xlsx
+++ b/artfynd/A 53366-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150399</v>
+        <v>121150398</v>
       </c>
       <c r="B2" t="n">
-        <v>92005</v>
+        <v>78343</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>749471</v>
+        <v>749391</v>
       </c>
       <c r="R2" t="n">
-        <v>7381290</v>
+        <v>7381398</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150398</v>
+        <v>121150399</v>
       </c>
       <c r="B3" t="n">
-        <v>78343</v>
+        <v>92005</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>749391</v>
+        <v>749471</v>
       </c>
       <c r="R3" t="n">
-        <v>7381398</v>
+        <v>7381290</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
